--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/atacama.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/atacama.xlsx
@@ -806,7 +806,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1505,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1570,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1818,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1883,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2009,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2257,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2505,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2692,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2818,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3127,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3253,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3318,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3383,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3631,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3757,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3883,11 @@
           <t>99.550.230-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3948,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4074,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4139,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4204,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4269,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4395,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4521,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4586,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4834,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4960,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5147,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5273,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5399,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5464,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5529,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5777,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5842,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5907,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6155,11 @@
           <t>77.430.568-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6281,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6407,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6533,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6659,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6907,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7094,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7220,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7285,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7655,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7781,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7846,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7911,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8281,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8407,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8472,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8537,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8602,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8789,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9098,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9407,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9533,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9842,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9907,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10094,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10220,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10346,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10411,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10537,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10602,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10789,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11037,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11224,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11411,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11598,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11724,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11850,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11915,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11980,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12167,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12293,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12602,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12850,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12915,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13102,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13228,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13415,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13602,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13667,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13732,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13797,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13862,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13927,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14114,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14179,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14244,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14309,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14496,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14561,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14687,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14752,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14817,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14882,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14947,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15378,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15443,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15630,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15695,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15760,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15825,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15890,11 @@
           <t>77.460.383-2</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16016,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16081,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16390,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16455,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16642,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16829,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16894,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16959,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17024,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17333,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17581,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17646,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17833,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18020,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18207,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18333,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18459,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18646,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18894,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +18959,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19024,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19150,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19276,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19402,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19589,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19715,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19841,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20333,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20398,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20524,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20589,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +20959,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21024,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21211,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21276,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21341,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21467,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21532,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21597,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21662,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21727,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21792,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21857,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22044,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22109,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22174,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22544,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22731,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22979,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23410,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23475,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23540,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23605,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23731,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +23918,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23983,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24109,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24174,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24239,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24365,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24491,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24556,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24682,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +24930,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +24995,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25243,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25674,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +25922,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26231,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26418,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +26483,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +26731,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +26796,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +26922,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +26987,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27113,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27300,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27365,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +27613,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +27861,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +27987,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28174,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28239,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28426,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28491,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +28739,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +28804,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +28869,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +28934,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +28999,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29064,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29312,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29377,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +29503,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29568,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +29816,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +29881,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30068,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30133,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30259,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30446,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +30572,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +30637,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +30885,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31011,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31137,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31202,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +31511,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +31637,11 @@
           <t>76.144.219-8</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +31702,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +31889,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32015,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32507,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32572,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +32698,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +32824,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +32950,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33015,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33080,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33267,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33393,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +33702,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34194,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34259,11 @@
           <t>77.056.974-5</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34324,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34389,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +34637,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +34702,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +34889,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35015,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +35568,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +35816,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +35942,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36129,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36194,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +36381,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +36446,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +36572,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +36637,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +36702,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +36828,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +36954,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37080,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37145,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37454,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +37580,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +37706,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +37832,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +37897,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38023,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38149,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38214,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +38340,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +38405,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +38470,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39206,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +39271,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38260,7 +39336,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +39462,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +39527,11 @@
           <t>77.883.662-9</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +39592,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +39657,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +39722,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +39909,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +39974,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +40161,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +40287,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39236,7 +40352,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +40417,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +40604,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +40669,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +40734,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +40860,11 @@
           <t>99.550.230-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +40925,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +40990,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +41177,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +41364,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +41551,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +41616,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +41742,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +42051,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +42177,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +42303,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41249,7 +42429,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41432,7 +42616,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41493,7 +42681,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +42746,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42042,7 +43238,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42103,7 +43303,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42286,7 +43490,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42591,7 +43799,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42713,7 +43925,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42774,7 +43990,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42957,7 +44177,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43018,7 +44242,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43140,7 +44368,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43201,7 +44433,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43384,7 +44620,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43628,7 +44868,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43872,7 +45116,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43994,7 +45242,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44116,7 +45368,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44604,7 +45860,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44848,7 +46108,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44970,7 +46234,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45153,7 +46421,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45397,7 +46669,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45458,7 +46734,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45702,7 +46982,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45824,7 +47108,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45885,7 +47173,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46129,7 +47421,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46251,7 +47547,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46556,7 +47856,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46678,7 +47982,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46800,7 +48108,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46983,7 +48295,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47044,7 +48360,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47349,7 +48669,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47471,7 +48795,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47593,7 +48921,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47837,7 +49169,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47959,7 +49295,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48020,7 +49360,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48081,7 +49425,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48325,7 +49673,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48630,7 +49982,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48691,7 +50047,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48752,7 +50112,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48874,7 +50238,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48935,7 +50303,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49057,7 +50429,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L797" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49240,7 +50616,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49362,7 +50742,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49423,7 +50807,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49484,7 +50872,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49606,7 +50998,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49789,7 +51185,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49850,7 +51250,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50277,7 +51681,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50338,7 +51746,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50460,7 +51872,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50582,7 +51998,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L822" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50765,7 +52185,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50887,7 +52311,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51253,7 +52681,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51497,7 +52929,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51619,7 +53055,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51680,7 +53120,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51741,7 +53185,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51802,7 +53250,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L842" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51985,7 +53437,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52900,7 +54356,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L860" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53083,7 +54543,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L863" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53144,7 +54608,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53205,7 +54673,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53388,7 +54860,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L868" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53449,7 +54925,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53571,7 +55051,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L871" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53632,7 +55116,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53754,7 +55242,11 @@
           <t>77.305.553-K</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53815,7 +55307,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L875" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54059,7 +55555,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54120,7 +55620,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L880" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54181,7 +55685,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54303,7 +55811,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54364,7 +55876,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54425,7 +55941,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54730,7 +56250,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54974,7 +56498,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55157,7 +56685,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55279,7 +56811,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55340,7 +56876,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55401,7 +56941,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55462,7 +57006,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55523,7 +57071,11 @@
           <t>77.305.553-K</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55767,7 +57319,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56072,7 +57628,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L912" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56133,7 +57693,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L913" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56194,7 +57758,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56438,7 +58006,11 @@
           <t>99.550.230-5</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L918" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56499,7 +58071,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L919" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56682,7 +58258,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56804,7 +58384,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56987,7 +58571,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L927" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57048,7 +58636,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57170,7 +58762,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L930" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57292,7 +58888,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L932" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57353,7 +58953,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57536,7 +59140,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L936" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57963,7 +59571,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58146,7 +59758,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58207,7 +59823,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58329,7 +59949,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58451,7 +60075,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L951" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58573,7 +60201,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L953" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58695,7 +60327,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K955" t="inlineStr"/>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L955" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58756,7 +60392,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L956" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59427,7 +61067,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59488,7 +61132,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L968" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59793,7 +61441,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L973" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59976,7 +61628,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L976" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60342,7 +61998,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L982" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60403,7 +62063,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L983" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60647,7 +62311,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K987" t="inlineStr"/>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L987" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60708,7 +62376,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K988" t="inlineStr"/>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L988" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60769,7 +62441,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L989" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60952,7 +62628,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L992" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61196,7 +62876,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K996" t="inlineStr"/>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L996" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61440,7 +63124,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1000" t="inlineStr"/>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1000" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61562,7 +63250,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1002" t="inlineStr"/>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1002" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61623,7 +63315,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1003" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61867,7 +63563,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K1007" t="inlineStr"/>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1007" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62050,7 +63750,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K1010" t="inlineStr"/>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1010" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62294,7 +63998,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1014" t="inlineStr"/>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1014" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62477,7 +64185,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1017" t="inlineStr"/>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1017" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62538,7 +64250,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1018" t="inlineStr"/>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1018" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62660,7 +64376,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1020" t="inlineStr"/>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1020" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62721,7 +64441,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K1021" t="inlineStr"/>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1021" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62843,7 +64567,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1023" t="inlineStr"/>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1023" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62965,7 +64693,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1025" t="inlineStr"/>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1025" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63392,7 +65124,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1032" t="inlineStr"/>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1032" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63575,7 +65311,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1035" t="inlineStr"/>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1035" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63697,7 +65437,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1037" t="inlineStr"/>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1037" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63880,7 +65624,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K1040" t="inlineStr"/>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1040" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63941,7 +65689,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1041" t="inlineStr"/>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1041" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64063,7 +65815,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K1043" t="inlineStr"/>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1043" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64124,7 +65880,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K1044" t="inlineStr"/>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1044" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64734,7 +66494,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1054" t="inlineStr"/>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1054" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64795,7 +66559,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K1055" t="inlineStr"/>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1055" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64856,7 +66624,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K1056" t="inlineStr"/>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1056" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65161,7 +66933,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K1061" t="inlineStr"/>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1061" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65405,7 +67181,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1065" t="inlineStr"/>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1065" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65527,7 +67307,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1067" t="inlineStr"/>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1067" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65710,7 +67494,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K1070" t="inlineStr"/>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1070" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66137,7 +67925,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1077" t="inlineStr"/>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1077" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66198,7 +67990,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1078" t="inlineStr"/>
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1078" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66320,7 +68116,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1080" t="inlineStr"/>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1080" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66503,7 +68303,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K1083" t="inlineStr"/>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1083" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66564,7 +68368,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1084" t="inlineStr"/>
+      <c r="K1084" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1084" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66747,7 +68555,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1087" t="inlineStr"/>
+      <c r="K1087" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1087" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66869,7 +68681,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1089" t="inlineStr"/>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1089" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66930,7 +68746,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1090" t="inlineStr"/>
+      <c r="K1090" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1090" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67113,7 +68933,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K1093" t="inlineStr"/>
+      <c r="K1093" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1093" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67296,7 +69120,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1096" t="inlineStr"/>
+      <c r="K1096" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1096" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67418,7 +69246,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1098" t="inlineStr"/>
+      <c r="K1098" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1098" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67601,7 +69433,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1101" t="inlineStr"/>
+      <c r="K1101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67662,7 +69498,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1102" t="inlineStr"/>
+      <c r="K1102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67784,7 +69624,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K1104" t="inlineStr"/>
+      <c r="K1104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67845,7 +69689,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K1105" t="inlineStr"/>
+      <c r="K1105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67906,7 +69754,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1106" t="inlineStr"/>
+      <c r="K1106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67967,7 +69819,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1107" t="inlineStr"/>
+      <c r="K1107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68394,7 +70250,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1114" t="inlineStr"/>
+      <c r="K1114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68821,7 +70681,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K1121" t="inlineStr"/>
+      <c r="K1121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69126,7 +70990,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1126" t="inlineStr"/>
+      <c r="K1126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69370,7 +71238,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K1130" t="inlineStr"/>
+      <c r="K1130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69431,7 +71303,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K1131" t="inlineStr"/>
+      <c r="K1131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69492,7 +71368,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1132" t="inlineStr"/>
+      <c r="K1132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69614,7 +71494,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1134" t="inlineStr"/>
+      <c r="K1134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69675,7 +71559,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1135" t="inlineStr"/>
+      <c r="K1135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69919,7 +71807,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1139" t="inlineStr"/>
+      <c r="K1139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -69980,7 +71872,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K1140" t="inlineStr"/>
+      <c r="K1140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70041,7 +71937,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K1141" t="inlineStr"/>
+      <c r="K1141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70102,7 +72002,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1142" t="inlineStr"/>
+      <c r="K1142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70163,7 +72067,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K1143" t="inlineStr"/>
+      <c r="K1143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70224,7 +72132,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K1144" t="inlineStr"/>
+      <c r="K1144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1144" t="inlineStr">
         <is>
           <t>USD</t>
